--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q40_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005768222678278589</v>
+        <v>0.000241518962354618</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005768222678278589</v>
+        <v>0.000241518962354618</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000544706125604136</v>
+        <v>0.0002256530579774999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000544706125604136</v>
+        <v>0.0002256530579774999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0006621431203177742</v>
+        <v>0.0002784849062407686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006621431203177742</v>
+        <v>0.0002784849062407686</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001042308896366567</v>
+        <v>0.0004449039474264553</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001042308896366567</v>
+        <v>0.0004449039474264553</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001597142517302916</v>
+        <v>0.0006823918699095166</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001597142517302916</v>
+        <v>0.0006823918699095166</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002171481021980714</v>
+        <v>0.0009231259268295918</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002171481021980714</v>
+        <v>0.0009231259268295918</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002918709928642075</v>
+        <v>0.001241274369073361</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002918709928642075</v>
+        <v>0.001241274369073361</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003628874535080122</v>
+        <v>0.001547269706708213</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003628874535080122</v>
+        <v>0.001547269706708213</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.004106877730227101</v>
+        <v>0.001752687358198861</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004106877730227101</v>
+        <v>0.001752687358198861</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004313683369915396</v>
+        <v>0.001839257639957153</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004313683369915396</v>
+        <v>0.001839257639957153</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004267760623792248</v>
+        <v>0.001816987649306238</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004267760623792248</v>
+        <v>0.001816987649306238</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004109576283103471</v>
+        <v>0.001748553613788214</v>
       </c>
       <c r="C13" t="n">
-        <v>0.004109576283103471</v>
+        <v>0.001748553613788214</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003907123569635028</v>
+        <v>0.001663242137068723</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003907123569635028</v>
+        <v>0.001663242137068723</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003632706795987703</v>
+        <v>0.001547114456935014</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003632706795987703</v>
+        <v>0.001547114456935014</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00352126408257326</v>
+        <v>0.001500836154212128</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00352126408257326</v>
+        <v>0.001500836154212128</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003289015796858888</v>
+        <v>0.001402910440082133</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003289015796858888</v>
+        <v>0.001402910440082133</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.003132777903849152</v>
+        <v>0.001337347675835128</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003132777903849152</v>
+        <v>0.001337347675835128</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.003179699819242084</v>
+        <v>0.001358325292556592</v>
       </c>
       <c r="C19" t="n">
-        <v>0.003179699819242084</v>
+        <v>0.001358325292556592</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.002956629595477839</v>
+        <v>0.001264427626999413</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002956629595477839</v>
+        <v>0.001264427626999413</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.002862504779123369</v>
+        <v>0.00122472020249875</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002862504779123369</v>
+        <v>0.00122472020249875</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
